--- a/healthcare_forms/044_doctor_diagnosis_form--healthcare_forms.xlsx
+++ b/healthcare_forms/044_doctor_diagnosis_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'cardiologist'}</t>
+          <t>cardiologist</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Cardiologist'}</t>
+          <t>Cardiologist</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'dermatologist'}</t>
+          <t>dermatologist</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Dermatologist'}</t>
+          <t>Dermatologist</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'endocrinologist'}</t>
+          <t>endocrinologist</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Endocrinologist'}</t>
+          <t>Endocrinologist</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'gastroenterologist'}</t>
+          <t>gastroenterologist</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Gastroenterologist'}</t>
+          <t>Gastroenterologist</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'general_practitioner'}</t>
+          <t>general_practitioner</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'General Practitioner'}</t>
+          <t>General Practitioner</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'nephrologist'}</t>
+          <t>nephrologist</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Nephrologist'}</t>
+          <t>Nephrologist</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'non-binary'}</t>
+          <t>non-binary</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Non-Binary'}</t>
+          <t>Non-Binary</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'signed'}</t>
+          <t>signed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Signed'}</t>
+          <t>Signed</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'unsighed'}</t>
+          <t>unsighed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Unsighed'}</t>
+          <t>Unsighed</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'not_signed'}</t>
+          <t>not_signed</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Not Signed'}</t>
+          <t>Not Signed</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'signed'}</t>
+          <t>signed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Signed'}</t>
+          <t>Signed</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'unsighed'}</t>
+          <t>unsighed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Unsighed'}</t>
+          <t>Unsighed</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'not_signed'}</t>
+          <t>not_signed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Not Signed'}</t>
+          <t>Not Signed</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'approved'}</t>
+          <t>approved</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'Approved'}</t>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'rejected'}</t>
+          <t>rejected</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Rejected'}</t>
+          <t>Rejected</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
